--- a/data/trans_dic/IP12B$hueso-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,43</t>
+          <t>0,0; 38,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,43</t>
+          <t>0,0; 25,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,29</t>
+          <t>0,0; 33,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,08</t>
+          <t>0,0; 39,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,53</t>
+          <t>0,0; 22,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 20,28</t>
+          <t>2,32; 20,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,13</t>
+          <t>0,0; 32,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 27,03</t>
+          <t>3,12; 23,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,21</t>
+          <t>0,0; 18,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,67</t>
+          <t>0,0; 29,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,79</t>
+          <t>0,0; 20,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,49</t>
+          <t>0,0; 26,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 20,98</t>
+          <t>2,4; 21,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 19,18</t>
+          <t>1,94; 19,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 18,32</t>
+          <t>1,9; 16,46</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,97</t>
+          <t>0,0; 20,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,36</t>
+          <t>0,0; 20,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,03</t>
+          <t>0,0; 16,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,62</t>
+          <t>0,0; 13,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,7</t>
+          <t>0,0; 44,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,05</t>
+          <t>0,0; 29,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 36,69</t>
+          <t>4,48; 39,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,8</t>
+          <t>0,0; 29,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 32,52</t>
+          <t>3,46; 29,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,94</t>
+          <t>0,0; 47,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,64</t>
+          <t>0,0; 25,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 23,61</t>
+          <t>4,2; 24,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 31,79</t>
+          <t>5,97; 31,4</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,91; 16,65</t>
+          <t>2,95; 16,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 13,9</t>
+          <t>2,72; 15,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 12,97</t>
+          <t>2,58; 13,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 15,09</t>
+          <t>1,78; 15,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 16,86</t>
+          <t>5,07; 17,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 14,22</t>
+          <t>1,46; 13,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 12,07</t>
+          <t>3,53; 12,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 12,84</t>
+          <t>4,83; 13,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 11,64</t>
+          <t>3,15; 10,96</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1569</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2181</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4712</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4375</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3935</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4026</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5427</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>634; 5569</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2573</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2627</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3878</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>598; 4594</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4700</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2868</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4079</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>678; 6023</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>647; 6433</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>681; 5897</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2575</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3671</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3409</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3674</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2253</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2899</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4419</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3687</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3021</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4625</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>645; 5701</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3085</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>731; 6168</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4364</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4337</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1539; 9000</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1411; 7418</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3398</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4335</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3546</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6051</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2768</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6302</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10386</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6314</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1294; 7435</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1665; 9378</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1420; 7590</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>830; 7190</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3225; 11208</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>699; 6273</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3197; 11372</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>6027; 16679</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3241; 11283</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$hueso-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,49</t>
+          <t>0,0; 31,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,52</t>
+          <t>0,0; 25,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,38</t>
+          <t>0,0; 28,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,42</t>
+          <t>0,0; 37,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,59</t>
+          <t>0,0; 19,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 20,36</t>
+          <t>2,29; 21,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,07</t>
+          <t>0,0; 32,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 23,95</t>
+          <t>3,24; 27,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,91</t>
+          <t>0,0; 19,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,11</t>
+          <t>0,0; 25,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,3</t>
+          <t>0,0; 19,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,22</t>
+          <t>0,0; 26,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 21,33</t>
+          <t>2,43; 21,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 19,31</t>
+          <t>1,94; 18,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 16,46</t>
+          <t>1,93; 18,55</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,28</t>
+          <t>0,0; 23,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,26</t>
+          <t>0,0; 20,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,25</t>
+          <t>0,0; 15,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,35</t>
+          <t>0,0; 15,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,14</t>
+          <t>0,0; 48,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,74</t>
+          <t>0,0; 30,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 39,63</t>
+          <t>4,35; 38,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,39</t>
+          <t>0,0; 26,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 29,22</t>
+          <t>3,47; 30,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,23</t>
+          <t>0,0; 45,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,01</t>
+          <t>0,0; 25,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 24,55</t>
+          <t>4,18; 24,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 31,4</t>
+          <t>5,7; 30,66</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 16,95</t>
+          <t>2,99; 17,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,3</t>
+          <t>2,54; 16,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 13,77</t>
+          <t>2,4; 14,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 15,39</t>
+          <t>1,53; 14,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 17,63</t>
+          <t>4,91; 17,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,11</t>
+          <t>1,45; 13,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 12,55</t>
+          <t>3,57; 12,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 13,36</t>
+          <t>5,06; 13,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 10,96</t>
+          <t>2,81; 10,86</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de huesos o de las articulaciones (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4712</t>
+          <t>0; 3882</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4375</t>
+          <t>0; 4308</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3935</t>
+          <t>0; 3368</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4026</t>
+          <t>0; 3842</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5427</t>
+          <t>0; 4784</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>634; 5569</t>
+          <t>626; 5884</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3878</t>
+          <t>0; 3897</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>598; 4594</t>
+          <t>621; 5193</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3835</t>
+          <t>0; 3917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4700</t>
+          <t>0; 4132</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2868</t>
+          <t>0; 2823</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4079</t>
+          <t>0; 4060</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>678; 6023</t>
+          <t>686; 6031</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>647; 6433</t>
+          <t>647; 6181</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>681; 5897</t>
+          <t>692; 6646</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2575</t>
+          <t>0; 2920</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3671</t>
+          <t>0; 3747</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3409</t>
+          <t>0; 3173</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3674</t>
+          <t>0; 4136</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3021</t>
+          <t>0; 3321</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4625</t>
+          <t>0; 4750</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>645; 5701</t>
+          <t>626; 5592</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3085</t>
+          <t>0; 2802</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>731; 6168</t>
+          <t>733; 6367</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4364</t>
+          <t>0; 4229</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4337</t>
+          <t>0; 4348</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1539; 9000</t>
+          <t>1531; 8813</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1411; 7418</t>
+          <t>1346; 7245</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1294; 7435</t>
+          <t>1310; 7500</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1665; 9378</t>
+          <t>1559; 9850</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1420; 7590</t>
+          <t>1321; 8031</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>830; 7190</t>
+          <t>713; 6839</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3225; 11208</t>
+          <t>3124; 10867</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>699; 6273</t>
+          <t>692; 6592</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3197; 11372</t>
+          <t>3234; 11278</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6027; 16679</t>
+          <t>6323; 17173</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3241; 11283</t>
+          <t>2894; 11188</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$hueso-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$hueso-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,27 +625,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,06%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,58%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,02%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,23%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,71</t>
+          <t>0,0; 28,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,13</t>
+          <t>0,0; 35,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,58</t>
+          <t>0,0; 25,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,63</t>
+          <t>0,0; 25,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,91</t>
+          <t>0,0; 19,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 21,51</t>
+          <t>2,31; 20,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,58%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>10,71%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>10,01%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>6,38%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,49%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,22</t>
+          <t>0,0; 29,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 27,07</t>
+          <t>0,0; 19,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,32</t>
+          <t>0,0; 26,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,59</t>
+          <t>0,0; 27,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,98</t>
+          <t>3,09; 27,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,1</t>
+          <t>0,0; 21,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,43; 21,36</t>
+          <t>2,41; 20,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 18,56</t>
+          <t>1,99; 19,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 18,55</t>
+          <t>1,85; 18,32</t>
         </is>
       </c>
     </row>
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,98%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,42 +898,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 23,36</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 24,97</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 20,68</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,13</t>
+          <t>0,0; 15,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,02</t>
+          <t>0,0; 13,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,74%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15,52%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>10,72%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>9,77%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15,66%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,51</t>
+          <t>0,0; 35,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,54</t>
+          <t>3,42; 32,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 38,87</t>
+          <t>0,0; 44,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,7</t>
+          <t>0,0; 54,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 30,17</t>
+          <t>0,0; 29,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,77</t>
+          <t>4,36; 36,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,08</t>
+          <t>0,0; 21,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,18; 24,04</t>
+          <t>4,46; 23,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 30,66</t>
+          <t>5,49; 31,79</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,74%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>7,07%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,43%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 17,09</t>
+          <t>1,5; 15,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 16,07</t>
+          <t>4,19; 16,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 14,57</t>
+          <t>1,4; 14,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,64</t>
+          <t>2,91; 16,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 17,1</t>
+          <t>2,48; 13,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,77</t>
+          <t>1,54; 12,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 12,45</t>
+          <t>3,64; 12,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 13,76</t>
+          <t>4,84; 12,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 10,86</t>
+          <t>2,74; 11,64</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,22 +1316,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1364,27 +1364,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>896</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3882</t>
+          <t>0; 3334</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4308</t>
+          <t>0; 3582</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3368</t>
+          <t>0; 3113</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3842</t>
+          <t>0; 4359</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4784</t>
+          <t>0; 4692</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>626; 5884</t>
+          <t>633; 5547</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1479,22 +1479,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1371</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1295</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1920</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1293</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1371</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1334</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3897</t>
+          <t>0; 4791</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>621; 5193</t>
+          <t>0; 2795</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3917</t>
+          <t>0; 4121</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4132</t>
+          <t>0; 3282</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2823</t>
+          <t>594; 5185</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4060</t>
+          <t>0; 4300</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>686; 6031</t>
+          <t>680; 5925</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>647; 6181</t>
+          <t>662; 6390</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>692; 6646</t>
+          <t>661; 6563</t>
         </is>
       </c>
     </row>
@@ -1637,27 +1637,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1690,27 +1690,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1743,42 +1743,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0; 4232</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3170</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3747</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3173</t>
+          <t>0; 3152</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4136</t>
+          <t>0; 3750</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2899</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1519</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2253</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2899</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1434</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3321</t>
+          <t>0; 3757</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4750</t>
+          <t>721; 6864</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>626; 5592</t>
+          <t>0; 4153</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2802</t>
+          <t>0; 3744</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>733; 6367</t>
+          <t>0; 4518</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4229</t>
+          <t>627; 5279</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4348</t>
+          <t>0; 3752</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1531; 8813</t>
+          <t>1634; 8655</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1346; 7245</t>
+          <t>1296; 7512</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2904</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6051</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2768</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>3398</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>4335</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3546</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2904</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6051</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2768</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1310; 7500</t>
+          <t>702; 7047</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1559; 9850</t>
+          <t>2662; 10719</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1321; 8031</t>
+          <t>669; 6806</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>713; 6839</t>
+          <t>1276; 7306</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3124; 10867</t>
+          <t>1521; 8522</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>692; 6592</t>
+          <t>846; 7152</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3234; 11278</t>
+          <t>3294; 10930</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6323; 17173</t>
+          <t>6044; 16026</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2894; 11188</t>
+          <t>2825; 11984</t>
         </is>
       </c>
     </row>
